--- a/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0003T0006Z000C1N25_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0003T0006Z000C1N25_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>16.69093381245899</v>
+        <v>2.712276744524587</v>
       </c>
       <c r="D2" t="n">
-        <v>18.87243548606661</v>
+        <v>3.066770766485824</v>
       </c>
       <c r="E2" t="n">
-        <v>14.01662018953318</v>
+        <v>2.277700780799141</v>
       </c>
       <c r="F2" t="n">
-        <v>12.01325309789918</v>
+        <v>1.952153628408617</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>10.67402020933643</v>
+        <v>1.73452828401717</v>
       </c>
       <c r="D3" t="n">
-        <v>11.37816684817326</v>
+        <v>1.848952112828155</v>
       </c>
       <c r="E3" t="n">
-        <v>14.01662018953318</v>
+        <v>2.277700780799141</v>
       </c>
       <c r="F3" t="n">
-        <v>12.01325309789918</v>
+        <v>1.952153628408617</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>40.9319015383163</v>
+        <v>6.651433999976399</v>
       </c>
       <c r="D4" t="n">
-        <v>34.60735451976046</v>
+        <v>5.623695109461075</v>
       </c>
       <c r="E4" t="n">
-        <v>14.01662018953318</v>
+        <v>2.277700780799141</v>
       </c>
       <c r="F4" t="n">
-        <v>12.01325309789918</v>
+        <v>1.952153628408617</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>41.83532166215858</v>
+        <v>6.798239770100769</v>
       </c>
       <c r="D5" t="n">
-        <v>41.49081837062548</v>
+        <v>6.742257985226641</v>
       </c>
       <c r="E5" t="n">
-        <v>14.01662018953318</v>
+        <v>2.277700780799141</v>
       </c>
       <c r="F5" t="n">
-        <v>12.01325309789918</v>
+        <v>1.952153628408617</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
